--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2501-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2501-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{200D134A-9BB5-4EF6-A58D-3FA86840FE66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4182F230-B684-4CAC-B2A3-8A12C03AD970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{CA995A4F-0DEB-4C8F-9944-E221AAC2660E}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{2ED2ADF2-C0AA-48BB-995A-F45B919DFAFF}"/>
   </bookViews>
   <sheets>
     <sheet name="2501-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1592,27 +1592,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97AE2E11-2576-4230-8F50-8705B8E77FA7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0454195E-53A3-4ABC-AF86-D7C13621EF84}">
   <dimension ref="A1:X54"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1646,7 +1645,7 @@
       <c r="W1" s="31"/>
       <c r="X1" s="23"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1682,7 +1681,7 @@
       <c r="W2" s="33"/>
       <c r="X2" s="34"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1734,7 +1733,7 @@
       </c>
       <c r="X3" s="37"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1802,7 +1801,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="38">
         <v>2024</v>
       </c>
@@ -1874,7 +1873,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="40">
         <v>2023</v>
       </c>
@@ -1946,7 +1945,7 @@
         <v>5.75</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="38">
         <v>2022</v>
       </c>
@@ -2018,7 +2017,7 @@
         <v>3.39</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="40">
         <v>2021</v>
       </c>
@@ -2090,7 +2089,7 @@
         <v>4.1500000000000004</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="38">
         <v>2020</v>
       </c>
@@ -2162,7 +2161,7 @@
         <v>5.41</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="40">
         <v>2019</v>
       </c>
@@ -2234,7 +2233,7 @@
         <v>6.62</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="38">
         <v>2018</v>
       </c>
@@ -2306,7 +2305,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="40">
         <v>2017</v>
       </c>
@@ -2378,7 +2377,7 @@
         <v>7.92</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="38">
         <v>2016</v>
       </c>
@@ -2450,7 +2449,7 @@
         <v>9.4</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="40">
         <v>2015</v>
       </c>
@@ -2522,7 +2521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="38">
         <v>2014</v>
       </c>
@@ -2594,7 +2593,7 @@
         <v>8.5500000000000007</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="40">
         <v>2013</v>
       </c>
@@ -2666,7 +2665,7 @@
         <v>6.56</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="38">
         <v>2012</v>
       </c>
@@ -2738,7 +2737,7 @@
         <v>7.12</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="40">
         <v>2011</v>
       </c>
@@ -2810,7 +2809,7 @@
         <v>9.9</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="38">
         <v>2010</v>
       </c>
@@ -2882,7 +2881,7 @@
         <v>5.35</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="40">
         <v>2009</v>
       </c>
@@ -2954,7 +2953,7 @@
         <v>4.6900000000000004</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="38">
         <v>2008</v>
       </c>
@@ -3026,7 +3025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="40">
         <v>2007</v>
       </c>
@@ -3098,7 +3097,7 @@
         <v>8.4700000000000006</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="38">
         <v>2006</v>
       </c>
@@ -3170,7 +3169,7 @@
         <v>5.64</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="40">
         <v>2005</v>
       </c>
@@ -3242,7 +3241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="38">
         <v>2004</v>
       </c>
@@ -3314,7 +3313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="40">
         <v>2003</v>
       </c>
@@ -3386,7 +3385,7 @@
         <v>1.34</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="38">
         <v>2002</v>
       </c>
@@ -3458,7 +3457,7 @@
         <v>7.6</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="40">
         <v>2001</v>
       </c>
@@ -3530,7 +3529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="38">
         <v>2000</v>
       </c>
@@ -3602,7 +3601,7 @@
         <v>8.1300000000000008</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="40">
         <v>1999</v>
       </c>
@@ -3674,7 +3673,7 @@
         <v>7.14</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="42">
         <v>1998</v>
       </c>
@@ -3746,7 +3745,7 @@
         <v>9.9</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="44"/>
       <c r="B32" s="45"/>
       <c r="C32" s="19" t="s">
@@ -3774,7 +3773,7 @@
       <c r="W32" s="51"/>
       <c r="X32" s="47"/>
     </row>
-    <row r="33" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="52">
         <v>1997</v>
       </c>
@@ -3846,7 +3845,7 @@
         <v>9.3800000000000008</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="54"/>
       <c r="B34" s="55"/>
       <c r="C34" s="21" t="s">
@@ -3874,7 +3873,7 @@
       <c r="W34" s="61"/>
       <c r="X34" s="57"/>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="38">
         <v>1996</v>
       </c>
@@ -3946,7 +3945,7 @@
         <v>5.16</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="52">
         <v>1995</v>
       </c>
@@ -4018,7 +4017,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="54"/>
       <c r="B37" s="55"/>
       <c r="C37" s="21" t="s">
@@ -4046,7 +4045,7 @@
       <c r="W37" s="61"/>
       <c r="X37" s="57"/>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="42">
         <v>1994</v>
       </c>
@@ -4118,7 +4117,7 @@
         <v>9.26</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="44"/>
       <c r="B39" s="45"/>
       <c r="C39" s="19" t="s">
@@ -4146,7 +4145,7 @@
       <c r="W39" s="51"/>
       <c r="X39" s="47"/>
     </row>
-    <row r="40" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="40">
         <v>1993</v>
       </c>
@@ -4218,7 +4217,7 @@
         <v>6.33</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="38">
         <v>1992</v>
       </c>
@@ -4290,7 +4289,7 @@
         <v>8.42</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="52">
         <v>1991</v>
       </c>
@@ -4362,7 +4361,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="54"/>
       <c r="B43" s="55"/>
       <c r="C43" s="21" t="s">
@@ -4390,7 +4389,7 @@
       <c r="W43" s="61"/>
       <c r="X43" s="57"/>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="42">
         <v>1990</v>
       </c>
@@ -4462,7 +4461,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="44"/>
       <c r="B45" s="45"/>
       <c r="C45" s="19" t="s">
@@ -4490,7 +4489,7 @@
       <c r="W45" s="51"/>
       <c r="X45" s="47"/>
     </row>
-    <row r="46" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="52">
         <v>1989</v>
       </c>
@@ -4562,7 +4561,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="54"/>
       <c r="B47" s="55"/>
       <c r="C47" s="21" t="s">
@@ -4590,7 +4589,7 @@
       <c r="W47" s="61"/>
       <c r="X47" s="57"/>
     </row>
-    <row r="48" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="38">
         <v>1988</v>
       </c>
@@ -4662,7 +4661,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="40">
         <v>1987</v>
       </c>
@@ -4734,7 +4733,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="38">
         <v>1986</v>
       </c>
@@ -4806,7 +4805,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="40">
         <v>1985</v>
       </c>
@@ -4878,7 +4877,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="38">
         <v>1984</v>
       </c>
@@ -4950,7 +4949,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="40">
         <v>1983</v>
       </c>
@@ -5022,7 +5021,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="38" t="s">
         <v>65</v>
       </c>
